--- a/artfynd/A 2761-2026 artfynd.xlsx
+++ b/artfynd/A 2761-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104159734</v>
+        <v>112606404</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>649402.3607507852</v>
+        <v>649402</v>
       </c>
       <c r="R2" t="n">
-        <v>7131117.951685081</v>
+        <v>7131118</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104159733</v>
+        <v>112605275</v>
       </c>
       <c r="B3" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>649402.3607507852</v>
+        <v>649516</v>
       </c>
       <c r="R3" t="n">
-        <v>7131117.951685081</v>
+        <v>7131107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,27 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,123 +876,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>109910591</v>
-      </c>
-      <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Nordanås, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>649516.1613263487</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7131107.379116777</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Fredrika</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2761-2026 artfynd.xlsx
+++ b/artfynd/A 2761-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606404</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>